--- a/processed_ruby_restored_xlsx/sc245_みるく７：天体観測.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc245_みるく７：天体観測.ss.xlsx
@@ -532,8 +532,8 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Concluding that, I spread out her futon in a corner of
-the Assembly Hall and lay down….</t>
+          <t>Concluding that, I spread out her futon in a corner
+of the Assembly Hall and lay down….</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -773,8 +773,8 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>When I quietly followed after her, Miru-chan went into
-the classroom by herself.</t>
+          <t>When I quietly followed after her, Miru-chan went
+into the classroom by herself.</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1137,8 +1137,8 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Even though I was touching over her clothes, something
-was clearly missing.</t>
+          <t>Even though I was touching over her clothes,
+something was clearly missing.</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1244,7 +1244,8 @@
       <c r="B52" s="1" t="inlineStr">
         <is>
           <t>Before I could say anything, Miru-chan suddenly
-started protesting that it wasn't what it looked like.</t>
+started protesting that it wasn't what it looked
+like.</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1425,7 +1426,8 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chan, shh... you'll wake everyone up, you know？」</t>
+          <t>「Miru-chan, shh... you'll wake everyone up, you
+know？」</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1486,7 +1488,8 @@
       <c r="B68" s="1" t="inlineStr">
         <is>
           <t>She probably thought that if she made a loud noise,
-the others sleeping in the assembly hall would notice.</t>
+the others sleeping in the assembly hall would
+notice.</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1886,8 +1889,8 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>This honesty is one of the things that makes Miru-chan
-so cute...！</t>
+          <t>This honesty is one of the things that makes
+Miru-chan so cute...！</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2341,8 +2344,8 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>Suppressing my wavering thoughts, I pinned them to the
-bulletin board.</t>
+          <t>Suppressing my wavering thoughts, I pinned them to
+the bulletin board.</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2556,8 +2559,8 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>When I instinctively try to press my crotch, Miru-chan
-presses her own between-her-legs and says,</t>
+          <t>When I instinctively try to press my crotch,
+Miru-chan presses her own between-her-legs and says,</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2587,8 +2590,8 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... my between-legs is all itchy... I'm gonna go
-to the bathroom, okay？」</t>
+          <t>「Nnngh... my between-legs is all itchy... I'm gonna
+go to the bathroom, okay？」</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2739,8 +2742,8 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>I didn't have the luxury of choosing my words anymore,
-so I blurted it out straight.</t>
+          <t>I didn't have the luxury of choosing my words
+anymore, so I blurted it out straight.</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -3091,8 +3094,8 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>I answered with everything I had, and ended up getting
-scolded by Miru-chan.</t>
+          <t>I answered with everything I had, and ended up
+getting scolded by Miru-chan.</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3759,7 +3762,8 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>「So you're really not trying to do anything weird...？」</t>
+          <t>「So you're really not trying to do anything
+weird...？」</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -4339,7 +4343,8 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan can't deny it or confirm it and just groans.</t>
+          <t>Miru-chan can't deny it or confirm it and just
+groans.</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4871,9 +4876,9 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>The place between her legs where Miru-chan was feeling
-the penis was, surprisingly, much more slippery than I
-expected.</t>
+          <t>The place between her legs where Miru-chan was
+feeling the penis was, surprisingly, much more
+slippery than I expected.</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4888,8 +4893,8 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>Of course — she'd been wiped down between her legs, so
-she’d gotten turned on...</t>
+          <t>Of course — she'd been wiped down between her legs,
+so she’d gotten turned on...</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -5192,7 +5197,8 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaaa...！ Ah, ah... aaah！ Haa, fuu... fufu！ Aahn...」</t>
+          <t>「Fuwaaa...！ Ah, ah... aaah！ Haa, fuu... fufu！
+Aahn...」</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5223,8 +5229,8 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>While firmly checking the feeling, I take the pleasure
-into my whole body and thrust my hips…！</t>
+          <t>While firmly checking the feeling, I take the
+pleasure into my whole body and thrust my hips…！</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5300,8 +5306,8 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chan... nn！ Those naughty sounds again... you're
-already wetting yourself, huh？」</t>
+          <t>「Miru-chan... nn！ Those naughty sounds again...
+you're already wetting yourself, huh？」</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5717,8 +5723,8 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>「Nnn！ The penis... it's coming... it's coming, ohhh...
-fuu, uuh...！」</t>
+          <t>「Nnn！ The penis... it's coming... it's coming,
+ohhh... fuu, uuh...！」</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5950,8 +5956,8 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>Because she closed her mouth, she tightened down there
-even more...</t>
+          <t>Because she closed her mouth, she tightened down
+there even more...</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -6074,8 +6080,8 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>But my aroused body is so maddening, I just can't hold
-it back.</t>
+          <t>But my aroused body is so maddening, I just can't
+hold it back.</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6151,9 +6157,9 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>Even though I told them to calm down earlier, they get
-even more worked up and a feel-good showdown breaks
-out.</t>
+          <t>Even though I told them to calm down earlier, they
+get even more worked up and a feel-good showdown
+breaks out.</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -6536,7 +6542,8 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>「Nnfu, fuffuu！ You told me to... do more, didn’t you？」</t>
+          <t>「Nnfu, fuffuu！ You told me to... do more, didn’t
+you？」</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6566,7 +6573,8 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>「I—I came, but… haa… nmm！ I—I have to hold back… nnn！」</t>
+          <t>「I—I came, but… haa… nmm！ I—I have to hold back…
+nnn！」</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6734,8 +6742,8 @@
       </c>
       <c r="B411" s="1" t="inlineStr">
         <is>
-          <t>I stroke it gently, gently so as not to hurt the small
-hole.</t>
+          <t>I stroke it gently, gently so as not to hurt the
+small hole.</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -6906,8 +6914,8 @@
       </c>
       <c r="B422" s="1" t="inlineStr">
         <is>
-          <t>Even as she gets angry, Miru-chan's hole keeps growing
-more and more heated.</t>
+          <t>Even as she gets angry, Miru-chan's hole keeps
+growing more and more heated.</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -7121,8 +7129,8 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>The effect is immediate: Miru-chan pants and trembles,
-her body convulsing.</t>
+          <t>The effect is immediate: Miru-chan pants and
+trembles, her body convulsing.</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -7152,8 +7160,8 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>「Is this... a weak spot？ You're already... starting to
-lose control again, huh？」</t>
+          <t>「Is this... a weak spot？ You're already... starting
+to lose control again, huh？」</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -7277,8 +7285,8 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>「Afu, nn... nngh！ Idiot, Onii-chan, you're an idiot...
-Miru's so embarrassed...！」</t>
+          <t>「Afu, nn... nngh！ Idiot, Onii-chan, you're an
+idiot... Miru's so embarrassed...！」</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -7709,8 +7717,8 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>「Just do it！ Wet yourself？ I'll pour you lots of tasty
-juice...！」</t>
+          <t>「Just do it！ Wet yourself？ I'll pour you lots of
+tasty juice...！」</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7772,8 +7780,9 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>On the contrary, she seems to be getting more and more
-aroused, and I'm getting turned on along with her...！</t>
+          <t>On the contrary, she seems to be getting more and
+more aroused, and I'm getting turned on along with
+her...！</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -7986,8 +7995,8 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>The penis twitches, making a pulsing sound as it pours
-a generous stream of semen in…</t>
+          <t>The penis twitches, making a pulsing sound as it
+pours a generous stream of semen in…</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8079,8 +8088,8 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>「Nnah！ Fuuu... nnngh！ Onii-chan's... semen suction, so
-much... nn！」</t>
+          <t>「Nnah！ Fuuu... nnngh！ Onii-chan's... semen suction,
+so much... nn！」</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -8386,8 +8395,8 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>「F-fuhfuu... ha！ Miru-chan... even if you swallow with
-your pussy, you still wet yourself, huh...」</t>
+          <t>「F-fuhfuu... ha！ Miru-chan... even if you swallow
+with your pussy, you still wet yourself, huh...」</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8448,9 +8457,9 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>It didn’t seem like the amount from just one time, and
-the penis still inside her pussy is hot and melting
-me.</t>
+          <t>It didn’t seem like the amount from just one time,
+and the penis still inside her pussy is hot and
+melting me.</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8831,8 +8840,8 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>Careful not to let Miru-chan fall over, I quietly pull
-out my penis.</t>
+          <t>Careful not to let Miru-chan fall over, I quietly
+pull out my penis.</t>
         </is>
       </c>
       <c r="C547" t="n">

--- a/processed_ruby_restored_xlsx/sc245_みるく７：天体観測.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc245_みるく７：天体観測.ss.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Huh, I wonder where she's going？</t>
+          <t>Huh, I wonder where they're going？</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>「…I-I did it…」</t>
+          <t>…I-I did it…</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1704,8 +1704,8 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Just when I thought she’d spoken honestly, her cheeks
-suddenly flushed bright red.</t>
+          <t>Just when I thought they’d spoke honestly, their
+cheeks suddenly flushed bright red.</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>I want to slip her into my pocket like this...</t>
+          <t>I want to slip them into my pocket like this...</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2607,7 +2607,7 @@
       <c r="B141" s="1" t="inlineStr">
         <is>
           <t>...Did she wet the bed and not wipe herself
-afterward...？</t>
+afterward...？"</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>「It'll be over soon, so hang in there…！」</t>
+          <t>It'll be over soon, so hang in there…！</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>「Is it—are you okay with this now？」</t>
+          <t>Is it—are you okay with this now？</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3762,8 +3762,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>「So you're really not trying to do anything
-weird...？」</t>
+          <t>So you're really not trying to do anything weird...？</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3793,8 +3792,8 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>「Ugh…！ No, it's just my imagination, just my
-imagination…！」</t>
+          <t>Ugh…！ No, it's just my imagination, just my
+imagination…！</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -4298,7 +4297,7 @@
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t>And then, I give her butt a quick pat...</t>
+          <t>And then, he gives her butt a quick pat...</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -5030,7 +5029,7 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>As I hesitated, Miru-chan moved toward me.</t>
+          <t>As he hesitated, Miru-chan moved toward him.</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5337,8 +5336,8 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... auuu, moooo... I just said I peed on
-purpose...！」</t>
+          <t>Nnngh... auuu, moooo... I just said I peed on
+purpose...！</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5368,7 +5367,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>「I didn't say that... ahaha...！」</t>
+          <t>I didn't say that... ahaha...！</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5661,8 +5660,8 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>Instead of moving much, I deeply thrust my penis in
-and rock back and forth.</t>
+          <t>Instead of moving much, he deeply thrusts his penis
+in and rocks back and forth.</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -5692,8 +5691,8 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>My penis pulsed along with her down there, sending
-twitching waves of pleasure.</t>
+          <t>Her penis pulsed down there too, sending twitching
+waves of pleasure.</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5723,8 +5722,8 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>「Nnn！ The penis... it's coming... it's coming,
-ohhh... fuu, uuh...！」</t>
+          <t>Nnn！ The penis... it's coming... it's coming, ohhh...
+fuu, uuh...！</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -6017,8 +6016,8 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>「Haa, fuu... haha, I'm feeling good, you know...
-fufuu...」</t>
+          <t>Haa, fuu... haha, I'm feeling good, you know...
+fufuu...</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -6573,8 +6572,7 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>「I—I came, but… haa… nmm！ I—I have to hold back…
-nnn！」</t>
+          <t>I—I came, but… haa… nmm！ I—I have to hold back… nnn！</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6727,7 +6725,7 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>「Nngh！ Nnh... ah... mmmph... mmm... nnh, ngh！」</t>
+          <t>Nngh！ Nnh... ah... mmmph... mmm... nnh, ngh！</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -6804,8 +6802,8 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>「Nngh! I—! I'm cumming... no, stop, nooo... nmph,
-nhah...!」</t>
+          <t>Nngh! I—! I'm cumming... no, stop, nooo... nmph,
+nhah...!</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -7223,7 +7221,7 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t>Each of those sounds drums in my head, pushing my
+          <t>Each of those sounds drums in his head, pushing his
 arousal up and up.</t>
         </is>
       </c>
@@ -7333,7 +7331,7 @@
         <is>
           <t>Her flustered, embarrassed movements make her hips
 sway awkwardly, which sends irregular stimulation to
-my penis.</t>
+his penis.</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7578,7 +7576,7 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>「Haaah！ Nnngh... ah！ No, no...！」</t>
+          <t>Haaah！ Nnngh... ah！ No, no...！</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -7608,7 +7606,7 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t>「Huh？　No...？」</t>
+          <t>Huh？　No...？</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -8627,8 +8625,8 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>With a face laid bare that looks like she's feeling
-good, she starts bobbing her head up and down...</t>
+          <t>With a face laid bare that looks like they're feeling
+good, they start bobbing their head up and down...</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8977,7 +8975,7 @@
       </c>
       <c r="B556" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan rubs her eyes but looks up at me.</t>
+          <t>Miru-chan rubs her eyes but looks up at him.</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -9097,7 +9095,7 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>Even just waking up, it seems she hasn’t forgotten
+          <t>Even just waking up, it seems they haven’t forgotten
 what happened last night.</t>
         </is>
       </c>
